--- a/data/sd-2024-general-statewide-results.xlsx
+++ b/data/sd-2024-general-statewide-results.xlsx
@@ -34,7 +34,7 @@
     <x:t>Precincts 691 of 691 Reporting (Precincts Partially Reported: 0/691)</x:t>
   </x:si>
   <x:si>
-    <x:t>Downloaded at 7/3/2026 6:05:07 PM</x:t>
+    <x:t>Downloaded at 7/3/2026 10:18:39 PM</x:t>
   </x:si>
   <x:si>
     <x:t>Presidential Electors</x:t>
